--- a/chinese_link_example_sentences_webscrape_main.xlsx
+++ b/chinese_link_example_sentences_webscrape_main.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanei\Documents\web design\WM lists\less flashy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanei\Documents\web design\chinese_study_app_corrected 9-17-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8265DE-25F3-4D61-9671-210F3961E87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE90457F-9109-450E-99A7-E5B2C2675839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="5460" windowWidth="17520" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="3" r:id="rId1"/>
@@ -3128,10 +3128,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>943</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
